--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L741"/>
+  <dimension ref="A1:L757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42516,7 +42516,11 @@
           <t>DM-9512044/2026</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr"/>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>9512044</t>
+        </is>
+      </c>
       <c r="C680" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43624,7 +43628,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B698" t="inlineStr"/>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C698" t="inlineStr">
         <is>
           <t>Obra 4</t>
@@ -43678,7 +43686,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B699" t="inlineStr"/>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C699" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43732,7 +43744,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B700" t="inlineStr"/>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C700" t="inlineStr">
         <is>
           <t>Obra 3</t>
@@ -43786,7 +43802,11 @@
           <t>DC-9511902/2026</t>
         </is>
       </c>
-      <c r="B701" t="inlineStr"/>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C701" t="inlineStr">
         <is>
           <t>Obra 2</t>
@@ -43840,7 +43860,11 @@
           <t>DM-9519034/2026</t>
         </is>
       </c>
-      <c r="B702" t="inlineStr"/>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
       <c r="C702" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -43894,7 +43918,11 @@
           <t>DC-9519020/2026</t>
         </is>
       </c>
-      <c r="B703" t="inlineStr"/>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>9519020</t>
+        </is>
+      </c>
       <c r="C703" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44010,7 +44038,11 @@
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B705" t="inlineStr"/>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>9519017</t>
+        </is>
+      </c>
       <c r="C705" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44064,7 +44096,11 @@
           <t>DC-9519295/2026</t>
         </is>
       </c>
-      <c r="B706" t="inlineStr"/>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>9519295</t>
+        </is>
+      </c>
       <c r="C706" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44118,7 +44154,11 @@
           <t>DC-9518140/2026</t>
         </is>
       </c>
-      <c r="B707" t="inlineStr"/>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>9518140</t>
+        </is>
+      </c>
       <c r="C707" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44234,7 +44274,11 @@
           <t>DM-007/2024-A</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr"/>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>9422060</t>
+        </is>
+      </c>
       <c r="C709" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44419,7 +44463,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -44429,12 +44473,12 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44444,22 +44488,22 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
@@ -44481,7 +44525,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -44491,12 +44535,12 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44506,22 +44550,22 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
@@ -44533,13 +44577,17 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B714" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -44549,12 +44597,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44564,33 +44612,41 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>26137308.02</t>
-        </is>
-      </c>
-      <c r="L714" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
-      <c r="B715" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C715" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44598,17 +44654,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44618,36 +44674,44 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>52753.74</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>1946.61</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>4690129.26</t>
-        </is>
-      </c>
-      <c r="L715" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B716" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -44657,12 +44721,12 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44672,33 +44736,41 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>36643741.73</t>
-        </is>
-      </c>
-      <c r="L716" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B717" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C717" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -44711,12 +44783,12 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44726,55 +44798,59 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387067.43</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69808.49</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>25215151.46</t>
-        </is>
-      </c>
-      <c r="L717" t="inlineStr"/>
+          <t>18527912.34</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44784,39 +44860,35 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>312620.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>9972.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>47037378.35</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>26137308.02</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44826,17 +44898,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44846,55 +44918,55 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>224948.57</t>
+          <t>52753.74</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>7175.84</t>
+          <t>1946.61</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>31475050.39</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>4690129.26</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
-        </is>
-      </c>
-      <c r="B720" t="inlineStr"/>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>9515457</t>
+        </is>
+      </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -44904,22 +44976,22 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>314158.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>10021.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>35675839.44</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="L720" t="inlineStr"/>
@@ -44927,12 +44999,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -44942,17 +45014,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -44962,39 +45034,35 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>1429560.95</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>45602.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>22005438.85</t>
-        </is>
-      </c>
-      <c r="L721" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>25215151.46</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -45009,12 +45077,12 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45024,22 +45092,22 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>291253.33</t>
+          <t>312620.08</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>9350.33</t>
+          <t>9972.54</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>31806746.63</t>
+          <t>47037378.35</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
@@ -45051,12 +45119,12 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45066,17 +45134,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45086,39 +45154,39 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>224948.57</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7175.84</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31475050.39</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -45128,17 +45196,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45148,37 +45216,37 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314158.69</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10021.63</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>35675839.44</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B725" t="inlineStr"/>
+          <t>DO-9481987/2025-L7</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>9481987</t>
+        </is>
+      </c>
       <c r="C725" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45186,17 +45254,17 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45206,35 +45274,39 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1429560.95</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45602.97</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>69497864.4</t>
-        </is>
-      </c>
-      <c r="L725" t="inlineStr"/>
+          <t>22005438.85</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -45244,17 +45316,17 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45264,39 +45336,39 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>6418794.48</t>
+          <t>291253.33</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>293904.2</t>
+          <t>9350.33</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>7845956.34</t>
+          <t>31806746.63</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -45306,57 +45378,61 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>3582262.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>483231.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>29521789.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B728" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C728" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45369,12 +45445,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -45384,12 +45460,12 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>2633312.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
@@ -45399,18 +45475,26 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>118166687.04</t>
-        </is>
-      </c>
-      <c r="L728" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B729" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C729" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45418,17 +45502,17 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -45438,12 +45522,12 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>1750547.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
@@ -45453,18 +45537,26 @@
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>12374450.41</t>
-        </is>
-      </c>
-      <c r="L729" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
-        </is>
-      </c>
-      <c r="B730" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C730" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45477,12 +45569,12 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Contorno de Andradas, em rodovia de contorno, sob jurisdição do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45492,7 +45584,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45507,18 +45599,26 @@
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>27896726.26</t>
-        </is>
-      </c>
-      <c r="L730" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B731" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C731" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45531,12 +45631,12 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -45546,12 +45646,12 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>271235.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
@@ -45561,10 +45661,14 @@
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>1497107.03</t>
-        </is>
-      </c>
-      <c r="L731" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -45584,42 +45688,42 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L732" t="inlineStr">
@@ -45646,42 +45750,42 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
@@ -45693,12 +45797,12 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -45708,17 +45812,17 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -45728,7 +45832,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45743,24 +45847,24 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -45770,17 +45874,17 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -45790,37 +45894,37 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>195614.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>6240.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>77703279.41</t>
-        </is>
-      </c>
-      <c r="L735" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>69497864.4</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B736" t="inlineStr"/>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>9497685</t>
+        </is>
+      </c>
       <c r="C736" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45828,17 +45932,17 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -45848,33 +45952,41 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>1334144.24</t>
+          <t>6418794.48</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>293904.2</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>42667985.76</t>
-        </is>
-      </c>
-      <c r="L736" t="inlineStr"/>
+          <t>7845956.34</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>2301762 000023/2025</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
-      <c r="B737" t="inlineStr"/>
+          <t>DM-005/2024-A</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>9414460</t>
+        </is>
+      </c>
       <c r="C737" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -45882,55 +45994,59 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3582262.51</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>483231.71</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>61779996.11</t>
-        </is>
-      </c>
-      <c r="L737" t="inlineStr"/>
+          <t>29521789.39</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -45940,17 +46056,17 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -45960,39 +46076,35 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>2061135.63</t>
+          <t>2633312.96</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>294133.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>22771327.58</t>
-        </is>
-      </c>
-      <c r="L738" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>118166687.04</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -46002,17 +46114,17 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -46022,39 +46134,35 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>3070543.84</t>
+          <t>1750547.98</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>453610.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>31351534.51</t>
-        </is>
-      </c>
-      <c r="L739" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>12374450.41</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -46064,17 +46172,17 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>Melhoramento e pavimentação do Contorno de Andradas, em rodovia de contorno, sob jurisdição do DER-MG</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -46084,87 +46192,1059 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>2983913.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>354928.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>27619284.46</t>
-        </is>
-      </c>
-      <c r="L740" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>27896726.26</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr"/>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>1768342.65</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>271235.62</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>1497107.03</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Supervisão</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>36033198.22</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>1131534.01</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>37164732.23</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>1347594.09</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>42988.22</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>35817138.14</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>45188997.86</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>77898894.3</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>195614.89</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>6240.1</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>77703279.41</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>9512043</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>44002130</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>1334144.24</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>42667985.76</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>9518942</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>2061135.63</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>294133.25</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>22771327.58</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>3070543.84</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>453610.76</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>31351534.51</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>2983913.41</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>354928.45</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>27619284.46</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B741" t="inlineStr">
+      <c r="B757" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D741" t="inlineStr">
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E741" t="inlineStr">
+      <c r="E757" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F741" t="inlineStr">
+      <c r="F757" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G741" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H741" t="inlineStr">
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I741" t="inlineStr">
+      <c r="I757" t="inlineStr">
         <is>
           <t>4953312.78</t>
         </is>
       </c>
-      <c r="J741" t="inlineStr">
+      <c r="J757" t="inlineStr">
         <is>
           <t>634447.12</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr">
+      <c r="K757" t="inlineStr">
         <is>
           <t>26219221.8</t>
         </is>
       </c>
-      <c r="L741" t="inlineStr">
+      <c r="L757" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L757"/>
+  <dimension ref="A1:L758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26263,17 +26263,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>4688649.35</t>
+          <t>4785597.45</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>487705.14</t>
+          <t>501500.83</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>2888272.75</t>
+          <t>2791324.65</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -29239,17 +29239,17 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>35168078.55</t>
+          <t>35684497.67</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>1734130.68</t>
+          <t>1774534.21</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>12466509.49</t>
+          <t>11950090.37</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -29425,17 +29425,17 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>23955698.78</t>
+          <t>24933809.56</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>1256170.71</t>
+          <t>1340956.63</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>21813247.67</t>
+          <t>20835136.89</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -29549,17 +29549,17 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>725068.34</t>
+          <t>732885.51</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>28858.97</t>
+          <t>29439</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>134700.67</t>
+          <t>126883.5</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -29727,17 +29727,17 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>3331025.61</t>
+          <t>3367947.02</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>145776.34</t>
+          <t>148363.15</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>7651376.16</t>
+          <t>7614454.75</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -29789,17 +29789,17 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>18835380.36</t>
+          <t>19434739.86</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>361589.34</t>
+          <t>392590.31</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>5571700.14</t>
+          <t>4972340.64</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -29913,17 +29913,17 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>86697687.08</t>
+          <t>91594516.94</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>3713387.39</t>
+          <t>3992360.41</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>65478542.65</t>
+          <t>60581712.79</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -30223,17 +30223,17 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>692584.47</t>
+          <t>721235.31</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>31985.57</t>
+          <t>34111.46</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>232099.95</t>
+          <t>203449.11</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -30347,17 +30347,17 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>48872991.4</t>
+          <t>49359783.39</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>1431563.47</t>
+          <t>1487173.29</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>3366656.53</t>
+          <t>2879864.54</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -31029,17 +31029,17 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>3575190.1</t>
+          <t>4404684.6</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>110895.06</t>
+          <t>140839.79</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>18883716.6</t>
+          <t>18054222.1</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -31339,17 +31339,17 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>12135963.53</t>
+          <t>15266736.18</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>327775</t>
+          <t>400117.45</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>34223947.8</t>
+          <t>31093175.15</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -31401,17 +31401,17 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>6488102.51</t>
+          <t>6967045.21</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>136070.63</t>
+          <t>148512.77</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>3146023.73</t>
+          <t>2667081.03</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -31463,17 +31463,17 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>4958818.11</t>
+          <t>5698711.16</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28559.85</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>18453077.09</t>
+          <t>17713184.04</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -31711,17 +31711,17 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>8468857.57</t>
+          <t>8637837.98</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>45389.91</t>
+          <t>49956.46</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>6150142.43</t>
+          <t>5981162.02</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -31773,17 +31773,17 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>6485277.62</t>
+          <t>7213960.5</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>139469.88</t>
+          <t>162714.86</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>15375208.78</t>
+          <t>14646525.9</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -31835,17 +31835,17 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>2093763.91</t>
+          <t>2423574.1</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>68577.92</t>
+          <t>80484.05</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>7316581.98</t>
+          <t>6986771.79</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -31897,17 +31897,17 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>2612713.79</t>
+          <t>2921464.5</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>84881.24</t>
+          <t>96027.12</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>6588074.08</t>
+          <t>6279323.37</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -32021,17 +32021,17 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>271191.66</t>
+          <t>273547.61</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>30379.5</t>
+          <t>30840.79</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>1089879.03</t>
+          <t>1087523.08</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -32383,12 +32383,12 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5969.69</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>1131117.06</t>
+          <t>1125147.37</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32403,7 +32403,7 @@
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>271937.4</t>
+          <t>265967.71</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -32569,12 +32569,12 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-233.8</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>1720953.51</t>
+          <t>1720719.71</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32589,7 +32589,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>210465.26</t>
+          <t>210231.46</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -35741,17 +35741,17 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>63183106.14</t>
+          <t>64324843.19</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>3977388.25</t>
+          <t>4064379.72</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>17373032.88</t>
+          <t>16231295.83</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
@@ -37291,17 +37291,17 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>27644019.13</t>
+          <t>28573278.26</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>1360250.95</t>
+          <t>1422787.18</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>19361551.42</t>
+          <t>18432292.29</t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -37353,17 +37353,17 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>28954461.09</t>
+          <t>29857616.38</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>1619393.95</t>
+          <t>1685409.29</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
         <is>
-          <t>22379294.24</t>
+          <t>21476138.95</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
@@ -37477,17 +37477,17 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>34430411.29</t>
+          <t>39180161.85</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>1677478.61</t>
+          <t>2056634.05</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>14701309.96</t>
+          <t>9951559.4</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
@@ -37787,17 +37787,17 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>1143238.64</t>
+          <t>1196093.25</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>55192.56</t>
+          <t>59114.37</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>341542.18</t>
+          <t>288687.57</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -37973,7 +37973,7 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>5129405.67</t>
+          <t>5178099.42</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>4755825.15</t>
+          <t>4707131.4</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -38903,17 +38903,17 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>36532892.05</t>
+          <t>37995174.55</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>999597.27</t>
+          <t>1109717</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>3797417.15</t>
+          <t>2335134.65</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -39275,17 +39275,17 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>4432629.82</t>
+          <t>5007832.17</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>192686.47</t>
+          <t>235941.04</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>3982869.99</t>
+          <t>3407667.64</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
@@ -39585,17 +39585,17 @@
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>493300.63</t>
+          <t>514686.48</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>27649.42</t>
+          <t>29516.4</t>
         </is>
       </c>
       <c r="K632" t="inlineStr">
         <is>
-          <t>310070.76</t>
+          <t>288684.91</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
@@ -39674,7 +39674,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -39724,7 +39724,7 @@
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
@@ -40143,17 +40143,17 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>12271758.41</t>
+          <t>15663917.87</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>246706.26</t>
+          <t>324655.09</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>39542817.03</t>
+          <t>36150657.57</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
@@ -40205,17 +40205,17 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>10363522.64</t>
+          <t>12142980.23</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>150290.55</t>
+          <t>192010.02</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>40597226.74</t>
+          <t>38817769.15</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -40267,17 +40267,17 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>25777210.17</t>
+          <t>28484932.26</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>543775.57</t>
+          <t>601170.03</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>27579581.55</t>
+          <t>24871859.46</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -40329,17 +40329,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>15936761.93</t>
+          <t>17455484.13</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>252163.94</t>
+          <t>292807.02</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>37305112.45</t>
+          <t>35786390.25</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -41375,17 +41375,17 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>987649.85</t>
+          <t>1151607.58</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>36736.25</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>2040399.11</t>
+          <t>1876441.38</t>
         </is>
       </c>
       <c r="L661" t="inlineStr">
@@ -41437,17 +41437,17 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>7564216.58</t>
+          <t>10212347.87</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>751469.95</t>
+          <t>952091.72</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>7740779.61</t>
+          <t>5092648.32</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -41685,17 +41685,17 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>40158557.52</t>
+          <t>41024155.64</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>1080082.85</t>
+          <t>1112047.61</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>6531698.16</t>
+          <t>5666100.04</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -41809,17 +41809,17 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>782885.1</t>
+          <t>934912.41</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>24974.01</t>
+          <t>29823.68</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>2404654.06</t>
+          <t>2252626.75</t>
         </is>
       </c>
       <c r="L668" t="inlineStr">
@@ -41871,17 +41871,17 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>566343.8</t>
+          <t>665425.59</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>18066.32</t>
+          <t>21227.02</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>3757941.88</t>
+          <t>3658860.09</t>
         </is>
       </c>
       <c r="L669" t="inlineStr">
@@ -42119,17 +42119,17 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>1356397.76</t>
+          <t>2131369.55</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>57908.74</t>
+          <t>96390.99</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
         <is>
-          <t>9263421.07</t>
+          <t>8488449.28</t>
         </is>
       </c>
       <c r="L673" t="inlineStr">
@@ -42181,17 +42181,17 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>116695.85</t>
+          <t>393026.33</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14399.44</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>4441123.79</t>
+          <t>4164793.31</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
@@ -42566,7 +42566,11 @@
           <t>11140838.3</t>
         </is>
       </c>
-      <c r="L680" t="inlineStr"/>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>2301762 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -42735,17 +42739,17 @@
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>2585676.73</t>
+          <t>3449475.83</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>75306.16</t>
+          <t>107180.34</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>20467005.95</t>
+          <t>19603206.85</t>
         </is>
       </c>
       <c r="L683" t="inlineStr">
@@ -43107,17 +43111,17 @@
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>1942640.46</t>
+          <t>2438875.29</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>206972.93</t>
+          <t>257680.32</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>31262421.94</t>
+          <t>30766187.11</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
@@ -43355,17 +43359,17 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>1488423.02</t>
+          <t>3037003.32</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>161209.54</t>
+          <t>294258.62</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>30324911.13</t>
+          <t>28776330.83</t>
         </is>
       </c>
       <c r="L693" t="inlineStr">
@@ -43479,17 +43483,17 @@
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>7951437.05</t>
+          <t>9349219.09</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>645406.28</t>
+          <t>749577.98</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>28999079.55</t>
+          <t>27601297.51</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
@@ -43603,17 +43607,17 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>2274880.49</t>
+          <t>3248018.95</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>230296.65</t>
+          <t>333625.77</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>32222894.63</t>
+          <t>31249756.17</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -43665,20 +43669,24 @@
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>277494.24</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16344.91</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>7919248.4</t>
-        </is>
-      </c>
-      <c r="L698" t="inlineStr"/>
+          <t>7641754.16</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -43723,20 +43731,24 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>5457.62</t>
+          <t>164883.75</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8833.11</t>
         </is>
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>4271941.93</t>
-        </is>
-      </c>
-      <c r="L699" t="inlineStr"/>
+          <t>4112515.8</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -43781,20 +43793,24 @@
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>148436.47</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8337.39</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>3773464.12</t>
-        </is>
-      </c>
-      <c r="L700" t="inlineStr"/>
+          <t>3625027.65</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -43852,7 +43868,11 @@
           <t>129370.06</t>
         </is>
       </c>
-      <c r="L701" t="inlineStr"/>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -43910,7 +43930,11 @@
           <t>46639997.64</t>
         </is>
       </c>
-      <c r="L702" t="inlineStr"/>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>2301762 000028/2025</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -43955,20 +43979,24 @@
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>715278.9</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46212</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>7088404.99</t>
-        </is>
-      </c>
-      <c r="L703" t="inlineStr"/>
+          <t>6373126.09</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>2301520 000027/2026</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -44088,7 +44116,11 @@
           <t>5995000</t>
         </is>
       </c>
-      <c r="L705" t="inlineStr"/>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>2301520 000017/2026</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -44146,7 +44178,11 @@
           <t>34487308.95</t>
         </is>
       </c>
-      <c r="L706" t="inlineStr"/>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>2301520 000023/2026</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -44204,37 +44240,41 @@
           <t>77916642.14</t>
         </is>
       </c>
-      <c r="L707" t="inlineStr"/>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>2301520 000007/2026</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-9521160/2026</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9521160</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+          <t>LOTE 6 - Execução de Micro revestimento asfáltico, sob jurisdição da 34ª URG Salinas com 320,10 km de extensão</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>35993836.02</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -44244,39 +44284,39 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>35993836.02</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>263469.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>87024.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>836254.5</t>
+          <t>35993836.02</t>
         </is>
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DM-9521156/2026</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9521156</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -44291,12 +44331,12 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
+          <t>LOTE 4 - Execução de Micro revestimento asfáltico, sob jurisdição da 28ª URG Teófilo Otoni  do DER-MG</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>11598999.99</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -44306,55 +44346,59 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>11598999.99</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>5246704.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>786995.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>36401486.16</t>
-        </is>
-      </c>
-      <c r="L709" t="inlineStr"/>
+          <t>11598999.99</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>2301762 000011/2026</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-9521185/2026</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9521185</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>Recup. Funcional do Pavimento na Rodovia MGC-455, trecho: Entrº BR-364 (Planura) - Pirajuba, com 24,10 Km de extensão - 25 URG - Uberaba do DER-MG</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>9149524.19</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -44364,7 +44408,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>9149524.19</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -44379,44 +44423,44 @@
       </c>
       <c r="K710" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>9149524.19</t>
         </is>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -44426,7 +44470,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -44441,29 +44485,29 @@
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DC-9518767/2026</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9518767</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -44473,12 +44517,12 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>Melhoramentos e pavimentação do trecho Ibertioga - Piedade do Rio Grande, na rodovia MG-338, com 13,200 km de extensão</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>41595728.1</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -44488,7 +44532,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>41595728.1</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -44503,44 +44547,44 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>41595728.1</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>1301606 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-9521162/2026</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9521162</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>LOTE 7 - Execução de Micro revestimento asfáltico, sob jurisdição da 39ª URG João Pinheiro com 100,00 km de extensão.</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>10148988.26</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -44550,7 +44594,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>10148988.26</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -44565,24 +44609,24 @@
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>10148988.26</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>VD - 9513687/2026</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9513687</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -44592,17 +44636,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>38006871.54</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -44612,39 +44656,39 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>38006871.54</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>38006871.54</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-9521166/2026</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9521166</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -44654,17 +44698,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>LOTE 2 - Execução de Micro revestimento asfáltico, sob jurisdição da 13ª URG Brasília de Minas com 232,70 km de extensão.</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>28699992.43</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -44674,39 +44718,39 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>28699992.43</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>28699992.43</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-9521157/2026</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9521157</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -44716,17 +44760,17 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>LOTE 5 - Execução de Micro revestimento asfáltico, sob jurisdição da 32ª URG Janaúba do DER-MG.</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>8719997.4</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -44736,39 +44780,39 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>8719997.4</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>8719997.4</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>VD - 9513695/2026</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9513695</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -44778,17 +44822,17 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>33096996.59</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -44798,59 +44842,59 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>33096996.59</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>387067.43</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>69808.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>18527912.34</t>
+          <t>33096996.59</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>VD-9513684/2026</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9513684</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
+          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>33293999.87</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -44860,7 +44904,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>33293999.87</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44875,20 +44919,24 @@
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>26137308.02</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr"/>
+          <t>33293999.87</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>2301001 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>DM-9521171/2026</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9521171</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -44898,17 +44946,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
+          <t>LOTE 1 - Execução de Micro revestimento asfáltico, sob jurisdição da 6ª URG - Montes Claros, com 154,00 km de extensão.</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>22350000</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -44918,35 +44966,39 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>22350000</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>52753.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>1946.61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>4690129.26</t>
-        </is>
-      </c>
-      <c r="L719" t="inlineStr"/>
+          <t>22350000</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>2301762 000011/2026</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -44956,17 +45008,17 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -44976,35 +45028,39 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>351190.37</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115998.15</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>36643741.73</t>
-        </is>
-      </c>
-      <c r="L720" t="inlineStr"/>
+          <t>748534.06</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>2301901 000003/2021</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -45014,17 +45070,17 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -45034,55 +45090,59 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5246704.23</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>786995.79</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>25215151.46</t>
-        </is>
-      </c>
-      <c r="L721" t="inlineStr"/>
+          <t>36401486.16</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -45092,59 +45152,59 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>312620.08</t>
+          <t>22988.6</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>9972.54</t>
+          <t>2641.32</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>47037378.35</t>
+          <t>9266777.14</t>
         </is>
       </c>
       <c r="L722" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45154,39 +45214,39 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>224948.57</t>
+          <t>22988.6</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>7175.84</t>
+          <t>2641.32</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>31475050.39</t>
+          <t>9266777.14</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -45196,17 +45256,17 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45216,35 +45276,39 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>314158.69</t>
+          <t>444194.29</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>10021.63</t>
+          <t>77630.35</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>35675839.44</t>
-        </is>
-      </c>
-      <c r="L724" t="inlineStr"/>
+          <t>18470785.48</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -45254,17 +45318,17 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45274,59 +45338,59 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>1429560.95</t>
+          <t>444194.29</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>45602.97</t>
+          <t>77630.35</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>22005438.85</t>
+          <t>18470785.48</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45336,39 +45400,39 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>291253.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>9350.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>31806746.63</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -45378,17 +45442,17 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -45398,44 +45462,44 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52753.74</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1946.61</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4690129.26</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -45445,12 +45509,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -45460,7 +45524,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -45475,24 +45539,24 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="L728" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -45507,12 +45571,12 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -45522,7 +45586,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -45537,24 +45601,24 @@
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DOV-002/2021-C</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -45564,17 +45628,17 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45584,7 +45648,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45599,24 +45663,24 @@
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="L730" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DOV-003/2021-C</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -45626,17 +45690,17 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -45646,7 +45710,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45661,24 +45725,24 @@
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="L731" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DOV-001/2021-C</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9292037</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -45688,17 +45752,17 @@
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -45708,7 +45772,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45723,24 +45787,24 @@
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DOV-004/2021-C</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9292043</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -45750,17 +45814,17 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11434972.74</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -45770,7 +45834,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11434972.74</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45785,24 +45849,24 @@
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11434972.74</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9521130/2026</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9521130</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -45812,17 +45876,17 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t xml:space="preserve">Elaboração de Análise de Conformidade para obra de arte especial - Ponte sobre o Rio São Francisco - Entr. MG/161 9 São Romão) - Entr. MG/ 161 (Porto </t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -45832,7 +45896,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45847,24 +45911,24 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000006/2026</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -45874,17 +45938,17 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -45894,35 +45958,39 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312620.08</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9972.54</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>69497864.4</t>
-        </is>
-      </c>
-      <c r="L735" t="inlineStr"/>
+          <t>47037378.35</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -45932,17 +46000,17 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -45952,39 +46020,39 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>6418794.48</t>
+          <t>339394.11</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>293904.2</t>
+          <t>10163.54</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>7845956.34</t>
+          <t>31360604.85</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -45994,59 +46062,59 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>3582262.51</t>
+          <t>314158.69</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>483231.71</t>
+          <t>10021.63</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>29521789.39</t>
+          <t>35675839.44</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -46056,17 +46124,17 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -46076,35 +46144,39 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>2633312.96</t>
+          <t>1429560.95</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45602.97</t>
         </is>
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>118166687.04</t>
-        </is>
-      </c>
-      <c r="L738" t="inlineStr"/>
+          <t>22005438.85</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -46114,17 +46186,17 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -46134,35 +46206,39 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>1750547.98</t>
+          <t>291253.33</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9350.33</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>12374450.41</t>
-        </is>
-      </c>
-      <c r="L739" t="inlineStr"/>
+          <t>31806746.63</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>9519740</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -46177,12 +46253,12 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Contorno de Andradas, em rodovia de contorno, sob jurisdição do DER-MG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -46192,7 +46268,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -46207,18 +46283,26 @@
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>27896726.26</t>
-        </is>
-      </c>
-      <c r="L740" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B741" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C741" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -46231,12 +46315,12 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -46246,12 +46330,12 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>271235.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
@@ -46261,20 +46345,24 @@
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>1497107.03</t>
-        </is>
-      </c>
-      <c r="L741" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -46284,59 +46372,59 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="L742" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -46346,59 +46434,59 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>11405231.61</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>514749.18</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>2859519.21</t>
         </is>
       </c>
       <c r="L743" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -46408,59 +46496,59 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>4198499.59</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>580458.91</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>28905552.31</t>
         </is>
       </c>
       <c r="L744" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -46470,59 +46558,59 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>2633312.96</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>118166687.04</t>
         </is>
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -46532,59 +46620,59 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>1750547.98</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>12374450.41</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -46594,61 +46682,57 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Melhoramento e pavimentação do Contorno de Andradas, em rodovia de contorno, sob jurisdição do DER-MG</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B748" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr"/>
       <c r="C748" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -46656,49 +46740,45 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>361647.49</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>1844.4</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>35817138.14</t>
-        </is>
-      </c>
-      <c r="L748" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>1406695.16</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -46743,17 +46823,17 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>1347594.09</t>
+          <t>2213059.16</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>42988.22</t>
+          <t>70596.55</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>35817138.14</t>
+          <t>34951673.07</t>
         </is>
       </c>
       <c r="L749" t="inlineStr">
@@ -46765,12 +46845,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -46780,59 +46860,59 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2213059.16</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70596.55</t>
         </is>
       </c>
       <c r="K750" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>34951673.07</t>
         </is>
       </c>
       <c r="L750" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -46847,12 +46927,12 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -46862,22 +46942,22 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>195614.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>6240.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>77703279.41</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L751" t="inlineStr">
@@ -46889,12 +46969,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -46904,17 +46984,17 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -46924,35 +47004,39 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>1334144.24</t>
+          <t>242773.31</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7744.45</t>
         </is>
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>42667985.76</t>
-        </is>
-      </c>
-      <c r="L752" t="inlineStr"/>
+          <t>77656120.99</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>9518942</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -46962,17 +47046,17 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -46982,12 +47066,12 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2125636.51</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
@@ -46997,20 +47081,24 @@
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>61779996.11</t>
-        </is>
-      </c>
-      <c r="L753" t="inlineStr"/>
+          <t>41876493.49</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>2301762 000004/2026</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9518942</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -47020,17 +47108,17 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>61779996.11</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -47040,39 +47128,39 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>61779996.11</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>2061135.63</t>
+          <t>13200.81</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>294133.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
         <is>
-          <t>22771327.58</t>
+          <t>61766795.3</t>
         </is>
       </c>
       <c r="L754" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -47087,12 +47175,12 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -47102,22 +47190,22 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>24832463.21</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>3070543.84</t>
+          <t>3384679.32</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>453610.76</t>
+          <t>500585.81</t>
         </is>
       </c>
       <c r="K755" t="inlineStr">
         <is>
-          <t>31351534.51</t>
+          <t>21447783.89</t>
         </is>
       </c>
       <c r="L755" t="inlineStr">
@@ -47129,12 +47217,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -47149,12 +47237,12 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -47164,22 +47252,22 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>34422078.35</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>2983913.41</t>
+          <t>5287270.54</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>354928.45</t>
+          <t>755994.33</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
         <is>
-          <t>27619284.46</t>
+          <t>29134807.81</t>
         </is>
       </c>
       <c r="L756" t="inlineStr">
@@ -47191,60 +47279,122 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>4288815.68</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>523252.41</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>26314382.19</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B758" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C757" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D757" t="inlineStr">
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E757" t="inlineStr">
+      <c r="E758" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F757" t="inlineStr">
+      <c r="F758" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G757" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H757" t="inlineStr">
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I757" t="inlineStr">
-        <is>
-          <t>4953312.78</t>
-        </is>
-      </c>
-      <c r="J757" t="inlineStr">
-        <is>
-          <t>634447.12</t>
-        </is>
-      </c>
-      <c r="K757" t="inlineStr">
-        <is>
-          <t>26219221.8</t>
-        </is>
-      </c>
-      <c r="L757" t="inlineStr">
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>6239363.38</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>777436.16</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>24933171.2</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L765"/>
+  <dimension ref="A1:L769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>52489165.84</t>
+          <t>53563188.43</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>46371151.46</t>
+          <t>47776144.31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5094437</t>
+          <t>4020414.41</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>6724996.26</t>
+          <t>7033743.86</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>7808493.21</t>
+          <t>8153427.1</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>760478.61</t>
+          <t>451731.01</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -29053,17 +29053,17 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>46331487.19</t>
+          <t>47459936.94</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>1829974.67</t>
+          <t>1925269.79</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>3925266.35</t>
+          <t>2796816.6</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -29239,17 +29239,17 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>35684497.67</t>
+          <t>39136213.89</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>1774534.21</t>
+          <t>1990485.16</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>11950090.37</t>
+          <t>8498374.15</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -29425,17 +29425,17 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>24933809.56</t>
+          <t>25964359.95</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>1340956.63</t>
+          <t>1428290.93</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>20835136.89</t>
+          <t>19804586.5</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -29549,17 +29549,17 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>732885.51</t>
+          <t>740702.69</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>29439</t>
+          <t>30019.03</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>126883.5</t>
+          <t>119066.32</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -30161,17 +30161,17 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>221081.14</t>
+          <t>300107.05</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>12735.12</t>
+          <t>18598.82</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>2319469.88</t>
+          <t>2240443.97</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -30223,17 +30223,17 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>721235.31</t>
+          <t>722629.29</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>34111.46</t>
+          <t>34214.89</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>203449.11</t>
+          <t>202055.13</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -30719,17 +30719,17 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>6653689.28</t>
+          <t>7237249.28</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>195820.91</t>
+          <t>216887.41</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>24218383.02</t>
+          <t>23634823.02</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -30905,17 +30905,17 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>3661472.63</t>
+          <t>4014913.7</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>110431.3</t>
+          <t>123190.5</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>5486461.62</t>
+          <t>5133020.55</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -31029,17 +31029,17 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>4404684.6</t>
+          <t>5153741.7</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>140839.79</t>
+          <t>167880.74</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>18054222.1</t>
+          <t>17305165</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -31153,17 +31153,17 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>6153166.63</t>
+          <t>6523003.03</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>24684.72</t>
+          <t>38128.73</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>935522.96</t>
+          <t>565686.56</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -31401,17 +31401,17 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>6967045.21</t>
+          <t>7374229.82</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>148512.77</t>
+          <t>158641.25</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>2667081.03</t>
+          <t>2259896.42</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -31463,17 +31463,17 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>5698711.16</t>
+          <t>6360964.51</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>28559.85</t>
+          <t>54122.81</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>17713184.04</t>
+          <t>17050930.69</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -31649,17 +31649,17 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>1355674.86</t>
+          <t>1885903.48</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10816.66</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>1046014.44</t>
+          <t>515785.82</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -31691,7 +31691,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Encabeçamento e ponte sobre o rio Paranaíba - Trecho Rochinha - Lagamar - Rodovia LMG-722 - extensão de 96,000m</t>
+          <t>Encabeçamento e ponte sobre o rio Paranaíba - Trecho Rocinha - Lagamar - Rodovia LMG-722 - extensão de 96,000m</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -31773,17 +31773,17 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>7213960.5</t>
+          <t>7942643.38</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>162714.86</t>
+          <t>185959.84</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>14646525.9</t>
+          <t>13917843.02</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -31835,17 +31835,17 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>2423574.1</t>
+          <t>2756966.34</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>80484.05</t>
+          <t>92519.49</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>6986771.79</t>
+          <t>6653379.55</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -31897,17 +31897,17 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>2921464.5</t>
+          <t>3221231.1</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>96027.12</t>
+          <t>106848.68</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>6279323.37</t>
+          <t>5979556.77</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -31959,17 +31959,17 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>204409.85</t>
+          <t>308118.77</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>12898.23</t>
+          <t>21879.42</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>1882173.67</t>
+          <t>1778464.75</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
@@ -35741,17 +35741,17 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>64324843.19</t>
+          <t>66933622</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>4064379.72</t>
+          <t>4455744.11</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>16231295.83</t>
+          <t>13622517.02</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
@@ -37043,17 +37043,17 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>567985.76</t>
+          <t>628698.52</t>
         </is>
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>58755.17</t>
+          <t>66817.82</t>
         </is>
       </c>
       <c r="K591" t="inlineStr">
         <is>
-          <t>1354658.52</t>
+          <t>1293945.76</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
@@ -37787,17 +37787,17 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>1196093.25</t>
+          <t>1378795.29</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>59114.37</t>
+          <t>72670.86</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>288687.57</t>
+          <t>105985.53</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -37973,7 +37973,7 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>5178099.42</t>
+          <t>5224474.42</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
@@ -37983,7 +37983,7 @@
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>4707131.4</t>
+          <t>4660756.4</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -38903,17 +38903,17 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>37995174.55</t>
+          <t>38703675.28</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>1109717</t>
+          <t>1182191.17</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>2335134.65</t>
+          <t>1626633.92</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -39213,17 +39213,17 @@
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>2511209.97</t>
+          <t>2766327.59</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>115495.23</t>
+          <t>131669.68</t>
         </is>
       </c>
       <c r="K626" t="inlineStr">
         <is>
-          <t>3263542.47</t>
+          <t>3008424.85</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
@@ -39585,17 +39585,17 @@
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>514686.48</t>
+          <t>517639.48</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>29516.4</t>
+          <t>29774.19</t>
         </is>
       </c>
       <c r="K632" t="inlineStr">
         <is>
-          <t>288684.91</t>
+          <t>285731.91</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
@@ -39674,7 +39674,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -39724,7 +39724,7 @@
       </c>
       <c r="L634" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
@@ -40143,17 +40143,17 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>15663917.87</t>
+          <t>16957725.13</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>324655.09</t>
+          <t>359772.91</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>36150657.57</t>
+          <t>34856850.31</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
@@ -40205,17 +40205,17 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>12142980.23</t>
+          <t>12844989.74</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>192010.02</t>
+          <t>204398.5</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>38817769.15</t>
+          <t>38115759.64</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -40329,17 +40329,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>17455484.13</t>
+          <t>18326581.96</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>292807.02</t>
+          <t>316047.83</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>35786390.25</t>
+          <t>34915292.42</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -40391,17 +40391,17 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>36559395.21</t>
+          <t>38585015.49</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>478298.63</t>
+          <t>521108.8</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>22739999.76</t>
+          <t>20714379.48</t>
         </is>
       </c>
       <c r="L645" t="inlineStr">
@@ -40515,17 +40515,17 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>728078.66</t>
+          <t>764098.64</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>20861.62</t>
+          <t>22161.94</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>927594.56</t>
+          <t>891574.58</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
@@ -40573,17 +40573,17 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>3426418.11</t>
+          <t>3810585.49</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>109802.42</t>
+          <t>123670.84</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>5857990.75</t>
+          <t>5473823.37</t>
         </is>
       </c>
       <c r="L648" t="inlineStr"/>
@@ -40631,17 +40631,17 @@
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>2406730.95</t>
+          <t>2738598</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>82341.16</t>
+          <t>94321.54</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>6811741.54</t>
+          <t>6479874.49</t>
         </is>
       </c>
       <c r="L649" t="inlineStr">
@@ -41189,17 +41189,17 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>6875341.48</t>
+          <t>7682661.83</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>1458717.17</t>
+          <t>1630080.21</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>11874590.29</t>
+          <t>11067269.94</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
@@ -41437,17 +41437,17 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>10212347.87</t>
+          <t>11861860.42</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>952091.72</t>
+          <t>1138016.01</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>5092648.32</t>
+          <t>3443135.77</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -41623,17 +41623,17 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>5030098.85</t>
+          <t>5716707.22</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>1072887.83</t>
+          <t>1219321.97</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>19462624.31</t>
+          <t>18776015.94</t>
         </is>
       </c>
       <c r="L665" t="inlineStr">
@@ -41685,17 +41685,17 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>41024155.64</t>
+          <t>41537392.26</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>1112047.61</t>
+          <t>1129206.87</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>5666100.04</t>
+          <t>5152863.42</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -41747,17 +41747,17 @@
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>2185024.19</t>
+          <t>2465330.87</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>463224.81</t>
+          <t>522649.8</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>7121606.01</t>
+          <t>6841299.33</t>
         </is>
       </c>
       <c r="L667" t="inlineStr">
@@ -42243,17 +42243,17 @@
       </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>5274217.04</t>
+          <t>6001177.26</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>686908.75</t>
+          <t>758877.43</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
         <is>
-          <t>7916775.85</t>
+          <t>7189815.63</t>
         </is>
       </c>
       <c r="L675" t="inlineStr">
@@ -42367,17 +42367,17 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>3109366.55</t>
+          <t>3174962.38</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>189728.8</t>
+          <t>194346.74</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>565412.89</t>
+          <t>499817.06</t>
         </is>
       </c>
       <c r="L677" t="inlineStr">
@@ -42739,17 +42739,17 @@
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>3449475.83</t>
+          <t>4187588.9</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>107180.34</t>
+          <t>134416.71</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>19603206.85</t>
+          <t>18865093.78</t>
         </is>
       </c>
       <c r="L683" t="inlineStr">
@@ -42801,17 +42801,17 @@
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>449949</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14298.7</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
         <is>
-          <t>3700000</t>
+          <t>3250051</t>
         </is>
       </c>
       <c r="L684" t="inlineStr">
@@ -42987,17 +42987,17 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>4748941.86</t>
+          <t>5994112.69</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
         <is>
-          <t>442770.62</t>
+          <t>623893.27</t>
         </is>
       </c>
       <c r="K687" t="inlineStr">
         <is>
-          <t>32205233.11</t>
+          <t>30960062.28</t>
         </is>
       </c>
       <c r="L687" t="inlineStr">
@@ -43049,17 +43049,17 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>592068.57</t>
+          <t>788208.98</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>3769.17</t>
+          <t>7770.42</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>4750514.31</t>
+          <t>4554373.9</t>
         </is>
       </c>
       <c r="L688" t="inlineStr">
@@ -43111,17 +43111,17 @@
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>2438875.29</t>
+          <t>2916873.59</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
         <is>
-          <t>257680.32</t>
+          <t>333620.31</t>
         </is>
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>30766187.11</t>
+          <t>30288188.81</t>
         </is>
       </c>
       <c r="L689" t="inlineStr">
@@ -43917,17 +43917,17 @@
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>566019.47</t>
+          <t>729020.54</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>36934.7</t>
+          <t>46105.76</t>
         </is>
       </c>
       <c r="K702" t="inlineStr">
         <is>
-          <t>46073978.17</t>
+          <t>45910977.1</t>
         </is>
       </c>
       <c r="L702" t="inlineStr">
@@ -44537,7 +44537,7 @@
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>728003.51</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
@@ -44547,7 +44547,7 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>9149524.19</t>
+          <t>8421520.68</t>
         </is>
       </c>
       <c r="L712" t="inlineStr">
@@ -44736,11 +44736,7 @@
           <t>41595728.1</t>
         </is>
       </c>
-      <c r="L715" t="inlineStr">
-        <is>
-          <t>1301606 000001/2026</t>
-        </is>
-      </c>
+      <c r="L715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -44785,7 +44781,7 @@
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>282654.72</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
@@ -44795,7 +44791,7 @@
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>10148988.26</t>
+          <t>9866333.54</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
@@ -45179,12 +45175,12 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>DM-9521426/2026</t>
+          <t>DM-9521171/2026</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>9521426</t>
+          <t>9521171</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -45194,17 +45190,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Rec. Func. MG-132 e MGC-265 / Pontos críticos MG-132 - 04 URG - Barbacena</t>
+          <t>LOTE 1 - Execução de Micro revestimento asfáltico, sob jurisdição da 6ª URG - Montes Claros, com 154,00 km de extensão.</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>47578995.64</t>
+          <t>22350000</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -45214,7 +45210,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>47578995.64</t>
+          <t>22350000</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -45229,44 +45225,44 @@
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>47578995.64</t>
+          <t>22350000</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>2301762 000009/2026</t>
+          <t>2301762 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-9521426/2026</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9521426</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+          <t>Rec. Func. MG-132 e MGC-265 / Pontos críticos MG-132 - 04 URG - Barbacena</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>47578995.64</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -45276,39 +45272,39 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>1099724.43</t>
+          <t>47578995.64</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>351190.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>115998.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>748534.06</t>
+          <t>47578995.64</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000009/2026</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DPEI-9520716/2026</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9520716</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -45318,17 +45314,17 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
+          <t>Pesquisa de Preços para Atualização dos Insumos de Edificações do Sistema de Custos e Orçamentos Referenciais de Obras e Serviços de Engenharia do Est</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>2549844</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -45338,39 +45334,39 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>41648190.39</t>
+          <t>2549844</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>8482903.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>1260901.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>33165286.83</t>
+          <t>2549844</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301601 000007/2026</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -45380,17 +45376,17 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -45400,59 +45396,59 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>1099724.43</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>22988.6</t>
+          <t>351190.37</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>2641.32</t>
+          <t>115998.15</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>9266777.14</t>
+          <t>748534.06</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 04ª URG</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -45462,27 +45458,27 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>9289765.74</t>
+          <t>41648190.39</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>22988.6</t>
+          <t>8482903.56</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>2641.32</t>
+          <t>1260901.12</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>9266777.14</t>
+          <t>33165286.83</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
@@ -45499,7 +45495,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -45509,12 +45505,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -45524,22 +45520,22 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>444194.29</t>
+          <t>22988.6</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>77630.35</t>
+          <t>2641.32</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>18470785.48</t>
+          <t>9266777.14</t>
         </is>
       </c>
       <c r="L728" t="inlineStr">
@@ -45561,7 +45557,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -45571,12 +45567,12 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -45586,22 +45582,22 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>444194.29</t>
+          <t>22988.6</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>77630.35</t>
+          <t>2641.32</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>18470785.48</t>
+          <t>9266777.14</t>
         </is>
       </c>
       <c r="L729" t="inlineStr">
@@ -45613,17 +45609,17 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -45633,12 +45629,12 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45648,39 +45644,39 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>666248.03</t>
+          <t>444194.29</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>41015.96</t>
+          <t>77630.35</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>25471059.99</t>
+          <t>18470785.48</t>
         </is>
       </c>
       <c r="L730" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -45690,17 +45686,17 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -45710,27 +45706,27 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>77611.93</t>
+          <t>444194.29</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>2863.87</t>
+          <t>77630.35</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>4665271.07</t>
+          <t>18470785.48</t>
         </is>
       </c>
       <c r="L731" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
@@ -45747,7 +45743,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -45757,12 +45753,12 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -45772,22 +45768,22 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>543643.26</t>
+          <t>666248.03</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>35267</t>
+          <t>41015.96</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>36100098.47</t>
+          <t>25471059.99</t>
         </is>
       </c>
       <c r="L732" t="inlineStr">
@@ -45799,12 +45795,12 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -45814,17 +45810,17 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -45834,59 +45830,59 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77611.93</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2863.87</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>4665271.07</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>DOV-002/2021-C</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>6759878.65</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -45896,39 +45892,39 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>6759878.65</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543643.26</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35267</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>6759878.65</t>
+          <t>36100098.47</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DOV-003/2021-C</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>9292042</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -45938,17 +45934,17 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>7705944.89</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -45958,7 +45954,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>7705944.89</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45973,24 +45969,24 @@
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>7705944.89</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DOV-001/2021-C</t>
+          <t>DPEI-9520827/2026</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>9292037</t>
+          <t>9520827</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -46000,17 +45996,17 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>EXECUÇÃO DE SERVIÇOS DE ESTUDOS TOPOGRÁFICOS (LEVANTAMENTO TOPOGRÁFICO PLANIALTIMÉTRICO E CADASTRAL) EM RODOVIAS SOB JURISDIÇÃO DO DER- MG EM TODO O E</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>10410721.35</t>
+          <t>1699613.8</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -46020,7 +46016,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>10410721.35</t>
+          <t>1699613.8</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -46035,24 +46031,24 @@
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>10410721.35</t>
+          <t>1699613.8</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301601 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DOV-004/2021-C</t>
+          <t>DPEI-9520825/2026</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9292043</t>
+          <t>9520825</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -46062,17 +46058,17 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>EXECUÇÃO DE SERVIÇOS DE ESTUDOS TOPOGRÁFICOS (LEVANTAMENTO TOPOGRÁFICO PLANIALTIMÉTRICO E CADASTRAL) EM RODOVIAS SOB JURISDIÇÃO DO DER- MG EM TODO O E</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>11434972.74</t>
+          <t>1629000</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -46082,7 +46078,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>11434972.74</t>
+          <t>1629000</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -46097,24 +46093,24 @@
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>11434972.74</t>
+          <t>1629000</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301601 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DC-9521130/2026</t>
+          <t>DOV-002/2021-C</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>9521130</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -46124,17 +46120,17 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração de Análise de Conformidade para obra de arte especial - Ponte sobre o Rio São Francisco - Entr. MG/161 9 São Romão) - Entr. MG/ 161 (Porto </t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>594297</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -46144,7 +46140,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>594297</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -46159,24 +46155,24 @@
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>594297</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>2301520 000006/2026</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DOV-003/2021-C</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -46196,7 +46192,7 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -46206,39 +46202,39 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>404668.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>12908.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>46945329.59</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="L739" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DOV-001/2021-C</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9292037</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -46253,12 +46249,12 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -46268,37 +46264,41 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>339394.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>10163.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>31360604.85</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="L740" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
-        </is>
-      </c>
-      <c r="B741" t="inlineStr"/>
+          <t>DOV-004/2021-C</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>9292043</t>
+        </is>
+      </c>
       <c r="C741" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -46311,12 +46311,12 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>11434972.74</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -46326,35 +46326,39 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>11434972.74</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>314158.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>10021.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>35675839.44</t>
-        </is>
-      </c>
-      <c r="L741" t="inlineStr"/>
+          <t>11434972.74</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>2301901 000008/2021</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DC-9521130/2026</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9521130</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -46364,17 +46368,17 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t xml:space="preserve">Elaboração de Análise de Conformidade para obra de arte especial - Ponte sobre o Rio São Francisco - Entr. MG/161 9 São Romão) - Entr. MG/ 161 (Porto </t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -46384,39 +46388,39 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>1908611.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>60884.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>21526388.57</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="L742" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000006/2026</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -46431,12 +46435,12 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -46446,22 +46450,22 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>291253.33</t>
+          <t>404668.84</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>9350.33</t>
+          <t>12908.89</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>31806746.63</t>
+          <t>46945329.59</t>
         </is>
       </c>
       <c r="L743" t="inlineStr">
@@ -46473,12 +46477,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -46488,17 +46492,17 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -46508,39 +46512,39 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>480555.72</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14613.73</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31219443.24</t>
         </is>
       </c>
       <c r="L744" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -46550,17 +46554,17 @@
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -46570,39 +46574,39 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>406660.48</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12972.43</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35583337.65</t>
         </is>
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>9519295</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -46612,17 +46616,17 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -46632,39 +46636,39 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1908611.23</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60884.67</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>21526388.57</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
         <is>
-          <t>2301520 000023/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -46674,17 +46678,17 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -46694,39 +46698,39 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>11405231.61</t>
+          <t>413021.56</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>514749.18</t>
+          <t>13243.17</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>2859519.21</t>
+          <t>31684978.4</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -46736,59 +46740,59 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>4198499.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>580458.91</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>28905552.31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L748" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -46798,17 +46802,17 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -46818,7 +46822,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46833,24 +46837,24 @@
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L749" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -46860,17 +46864,17 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
+          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -46880,7 +46884,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46895,24 +46899,24 @@
       </c>
       <c r="K750" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="L750" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>DM-9437231-A</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>9437231</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -46922,17 +46926,17 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 02ª URG</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>48698697.21</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -46942,39 +46946,39 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>48698697.21</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11405231.61</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514749.18</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>48698697.21</t>
+          <t>2859519.21</t>
         </is>
       </c>
       <c r="L751" t="inlineStr">
         <is>
-          <t>2301762 000006/2024</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -46984,59 +46988,59 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>5110057.88</t>
+          <t>5091753.23</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>139646.47</t>
+          <t>731575.94</t>
         </is>
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>115689942.12</t>
+          <t>28012298.67</t>
         </is>
       </c>
       <c r="L752" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -47046,17 +47050,17 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -47066,39 +47070,39 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>2351350.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
         <is>
-          <t>32105.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>11773648.05</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="L753" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>9519740</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -47108,17 +47112,17 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Contorno de Andradas, em rodovia de contorno, sob jurisdição do DER-MG</t>
+          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -47128,7 +47132,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -47143,22 +47147,26 @@
       </c>
       <c r="K754" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="L754" t="inlineStr">
         <is>
-          <t>2301520 000040/2026</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B755" t="inlineStr"/>
+          <t>DM-9437231-A</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>9437231</t>
+        </is>
+      </c>
       <c r="C755" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -47166,17 +47174,17 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 02ª URG</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>48698697.21</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -47186,35 +47194,39 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>48698697.21</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>361647.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>1844.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K755" t="inlineStr">
         <is>
-          <t>1406695.16</t>
-        </is>
-      </c>
-      <c r="L755" t="inlineStr"/>
+          <t>48698697.21</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>2301762 000006/2024</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -47224,59 +47236,59 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>2213059.16</t>
+          <t>5110057.88</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>70596.55</t>
+          <t>139646.47</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
         <is>
-          <t>34951673.07</t>
+          <t>115689942.12</t>
         </is>
       </c>
       <c r="L756" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -47286,59 +47298,59 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>2213059.16</t>
+          <t>3294350.69</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>70596.55</t>
+          <t>82624.61</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>34951673.07</t>
+          <t>10830647.7</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -47348,17 +47360,17 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>Melhoramento e pavimentação do Contorno de Andradas, em rodovia de contorno, sob jurisdição do DER-MG</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -47368,7 +47380,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -47383,26 +47395,22 @@
       </c>
       <c r="K758" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="L758" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
-        </is>
-      </c>
-      <c r="B759" t="inlineStr">
-        <is>
-          <t>9482014</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr"/>
       <c r="C759" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -47410,17 +47418,17 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -47430,39 +47438,35 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>467698.96</t>
+          <t>361647.49</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>15952.15</t>
+          <t>1844.4</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
         <is>
-          <t>77431195.34</t>
-        </is>
-      </c>
-      <c r="L759" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+          <t>1406695.16</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -47472,59 +47476,59 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>2125636.51</t>
+          <t>2915216.97</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92995.38</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>41876493.49</t>
+          <t>34249515.26</t>
         </is>
       </c>
       <c r="L760" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>9518942</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -47534,59 +47538,59 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>13200.81</t>
+          <t>2915216.97</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92995.38</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
         <is>
-          <t>61766795.3</t>
+          <t>34249515.26</t>
         </is>
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -47596,17 +47600,17 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -47616,39 +47620,39 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>3372755.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>498844.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>21459707.49</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -47658,17 +47662,17 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -47678,39 +47682,39 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>5287270.54</t>
+          <t>467698.96</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>755994.33</t>
+          <t>15952.15</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>29134807.81</t>
+          <t>77431195.34</t>
         </is>
       </c>
       <c r="L763" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -47725,12 +47729,12 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -47740,87 +47744,335 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>4288815.68</t>
+          <t>2125636.51</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>523252.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
         <is>
-          <t>26314382.19</t>
+          <t>41876493.49</t>
         </is>
       </c>
       <c r="L764" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>9518942</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Rodovia</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>61779996.11</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>13200.81</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>61766795.3</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>2301520 000011/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>4336664.12</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>654013.33</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>20495799.09</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>7934404.13</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>1101483.73</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>26487674.22</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>5874286.21</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>751156.76</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>24728911.66</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B765" t="inlineStr">
+      <c r="B769" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D765" t="inlineStr">
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E765" t="inlineStr">
+      <c r="E769" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F765" t="inlineStr">
+      <c r="F769" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G765" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H765" t="inlineStr">
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I765" t="inlineStr">
-        <is>
-          <t>6239363.38</t>
-        </is>
-      </c>
-      <c r="J765" t="inlineStr">
-        <is>
-          <t>777436.16</t>
-        </is>
-      </c>
-      <c r="K765" t="inlineStr">
-        <is>
-          <t>24933171.2</t>
-        </is>
-      </c>
-      <c r="L765" t="inlineStr">
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>6708321.8</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>857116.51</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>24464212.78</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>

--- a/upload/obra.xlsx
+++ b/upload/obra.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L769"/>
+  <dimension ref="A1:L772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23535,17 +23535,17 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>30705217.64</t>
+          <t>30743464.63</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>1669907.23</t>
+          <t>1675965.55</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>5550685.93</t>
+          <t>5512438.94</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -23597,17 +23597,17 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>8142523</t>
+          <t>8620593.03</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>612904.68</t>
+          <t>659584.75</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>26193088.48</t>
+          <t>25715018.45</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -26263,17 +26263,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>4785597.45</t>
+          <t>4871445.52</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>501500.83</t>
+          <t>513716.99</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>2791324.65</t>
+          <t>2705476.58</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -28929,17 +28929,17 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>2889629.46</t>
+          <t>2990966.07</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>261555.11</t>
+          <t>274647.8</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>456069.67</t>
+          <t>354733.06</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -29363,17 +29363,17 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>43557540.92</t>
+          <t>45703879.83</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>2201189.62</t>
+          <t>2345549.85</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>9601247.93</t>
+          <t>7454909.02</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -29487,17 +29487,17 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>35313102.22</t>
+          <t>38561295.04</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>1791888.48</t>
+          <t>1997273.28</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>12845502.99</t>
+          <t>9597310.17</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
@@ -29633,10 +29633,14 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC-9441355/2024 </t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr"/>
+          <t>DC-9441355/2024</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>9441355</t>
+        </is>
+      </c>
       <c r="C472" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -29682,7 +29686,11 @@
           <t>2808049.54</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr"/>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>2301520 000014/2024</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -29727,17 +29735,17 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>3367947.02</t>
+          <t>3382233.58</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>148363.15</t>
+          <t>149174.89</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>7614454.75</t>
+          <t>7600168.19</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -29913,17 +29921,17 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>91594516.94</t>
+          <t>96306069.47</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>3992360.41</t>
+          <t>4235549.92</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>60581712.79</t>
+          <t>55870160.26</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -30099,17 +30107,17 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>6656366.86</t>
+          <t>7116347.65</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>616068.24</t>
+          <t>660474.48</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4263509.37</t>
+          <t>3803528.58</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
@@ -30285,17 +30293,17 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>5598958.11</t>
+          <t>5634270.7</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>158852.76</t>
+          <t>162146.9</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>1754271.6</t>
+          <t>1718959.01</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -30347,17 +30355,17 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>49359783.39</t>
+          <t>49866340.76</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>1487173.29</t>
+          <t>1527345.32</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>2879864.54</t>
+          <t>2373307.17</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -30595,17 +30603,17 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>6449379.37</t>
+          <t>6561191.79</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>204263.73</t>
+          <t>213012.05</t>
         </is>
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>5752654.19</t>
+          <t>5640841.77</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
@@ -30657,17 +30665,17 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>38208071.57</t>
+          <t>39206923.04</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>561423.69</t>
+          <t>601023.59</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>5581284.31</t>
+          <t>4582432.84</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -30781,17 +30789,17 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>4127010.8</t>
+          <t>4402268.35</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>1229351.25</t>
+          <t>1321111.83</t>
         </is>
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>6237100.67</t>
+          <t>5961843.12</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -30967,17 +30975,17 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>7949156.18</t>
+          <t>8552924.2</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>144231.02</t>
+          <t>158668.51</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>36623843.82</t>
+          <t>36020075.8</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -31339,17 +31347,17 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>15266736.18</t>
+          <t>17706388.56</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>400117.45</t>
+          <t>456702.98</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>31093175.15</t>
+          <t>28653522.77</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -32641,17 +32649,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>113638.28</t>
+          <t>130562.84</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>11884.47</t>
+          <t>15198.29</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>297345.12</t>
+          <t>280420.56</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -37229,17 +37237,17 @@
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>42096948.44</t>
+          <t>45638923.67</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>2028372.53</t>
+          <t>2256794.25</t>
         </is>
       </c>
       <c r="K594" t="inlineStr">
         <is>
-          <t>5658450.58</t>
+          <t>2116475.35</t>
         </is>
       </c>
       <c r="L594" t="inlineStr">
@@ -37353,17 +37361,17 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>29857616.38</t>
+          <t>35544952.11</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>1685409.29</t>
+          <t>2074587.66</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
         <is>
-          <t>21476138.95</t>
+          <t>15788803.22</t>
         </is>
       </c>
       <c r="L596" t="inlineStr">
@@ -37415,17 +37423,17 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>32788025.05</t>
+          <t>35428859.69</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>1752186.32</t>
+          <t>1926400.93</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
         <is>
-          <t>17274029.23</t>
+          <t>14633194.59</t>
         </is>
       </c>
       <c r="L597" t="inlineStr">
@@ -37477,17 +37485,17 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>39180161.85</t>
+          <t>43110679.3</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>2056634.05</t>
+          <t>2298280.74</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>11960194.06</t>
+          <t>8029676.61</t>
         </is>
       </c>
       <c r="L598" t="inlineStr">
@@ -37601,17 +37609,17 @@
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>41131297.31</t>
+          <t>45946779.1</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>2025567.66</t>
+          <t>2321593.09</t>
         </is>
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>12861489.47</t>
+          <t>8046007.68</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
@@ -38717,17 +38725,17 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>3629949.28</t>
+          <t>3642689.54</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>275296.43</t>
+          <t>276488.71</t>
         </is>
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t>2142916.46</t>
+          <t>2130176.2</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
@@ -39089,17 +39097,17 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>649910.54</t>
+          <t>729931.11</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>75635.28</t>
+          <t>86262.01</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>9010086.54</t>
+          <t>8930065.97</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
@@ -39275,17 +39283,17 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>5007832.17</t>
+          <t>5586023.13</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>235941.04</t>
+          <t>285820.98</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>4184093.78</t>
+          <t>3605902.82</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
@@ -39647,17 +39655,17 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>7311557.61</t>
+          <t>7760020.71</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>2169828.84</t>
+          <t>2319224.09</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>6622490.77</t>
+          <t>6174027.67</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
@@ -39709,17 +39717,17 @@
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>4249837.74</t>
+          <t>4516295.33</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>1268213.67</t>
+          <t>1357089.91</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t>4855059.67</t>
+          <t>4588602.08</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
@@ -39771,17 +39779,17 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>6628686.35</t>
+          <t>7052275.65</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>1970219.65</t>
+          <t>2111306.08</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>8648054.74</t>
+          <t>8224465.44</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
@@ -39895,17 +39903,17 @@
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t>12853940.75</t>
+          <t>14792977.09</t>
         </is>
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>188795.5</t>
+          <t>225961</t>
         </is>
       </c>
       <c r="K637" t="inlineStr">
         <is>
-          <t>36239598.7</t>
+          <t>34300562.36</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
@@ -40081,17 +40089,17 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>5628407.22</t>
+          <t>5709098.66</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>123056.75</t>
+          <t>125494.59</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>5837987.45</t>
+          <t>5757296.01</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
@@ -40267,17 +40275,17 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>28484932.26</t>
+          <t>31668923</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>601170.03</t>
+          <t>680224.19</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>24871859.46</t>
+          <t>21687868.72</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -40453,17 +40461,17 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>31850048.82</t>
+          <t>36411361.91</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>665409.61</t>
+          <t>762416.53</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>21723951.17</t>
+          <t>17162638.08</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -40537,10 +40545,14 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
-        </is>
-      </c>
-      <c r="B648" t="inlineStr"/>
+          <t>AEST-9469794/2025</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>9469794</t>
+        </is>
+      </c>
       <c r="C648" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -40586,7 +40598,11 @@
           <t>5473823.37</t>
         </is>
       </c>
-      <c r="L648" t="inlineStr"/>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>2301931 000002/2025</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -40693,17 +40709,17 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>17357932.93</t>
+          <t>22416296.19</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>469618.45</t>
+          <t>581010.24</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>47626372.41</t>
+          <t>42568009.15</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -40755,17 +40771,17 @@
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>11767615.78</t>
+          <t>12571369.93</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>1149808.84</t>
+          <t>1253600.39</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>2937281.13</t>
+          <t>2133526.98</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -40879,17 +40895,17 @@
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>870846.3</t>
+          <t>1014931.41</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>25884.47</t>
+          <t>30480.78</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>1754062.79</t>
+          <t>1609977.68</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -41003,17 +41019,17 @@
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>8575171.1</t>
+          <t>10565584.29</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>839278.13</t>
+          <t>1022699.02</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>6142030.88</t>
+          <t>4151617.69</t>
         </is>
       </c>
       <c r="L655" t="inlineStr">
@@ -41127,17 +41143,17 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>7582078.01</t>
+          <t>8662414.76</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>709787.92</t>
+          <t>791889.3</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>4577195.82</t>
+          <t>3496859.07</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -41313,17 +41329,17 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>1958270.54</t>
+          <t>2109998.79</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>420561.31</t>
+          <t>453140.49</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>12971076.41</t>
+          <t>12819348.16</t>
         </is>
       </c>
       <c r="L660" t="inlineStr">
@@ -41375,17 +41391,17 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>1151607.58</t>
+          <t>1319521.33</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>36736.25</t>
+          <t>42092.69</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>1876441.38</t>
+          <t>1708527.63</t>
         </is>
       </c>
       <c r="L661" t="inlineStr">
@@ -41499,17 +41515,17 @@
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>4749005.75</t>
+          <t>5146017.93</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>106093.22</t>
+          <t>130922.57</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>1450724.01</t>
+          <t>1053711.83</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
@@ -41561,17 +41577,17 @@
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>8703154.6</t>
+          <t>9871453.56</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>374977.19</t>
+          <t>432997.96</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
         <is>
-          <t>2226820.96</t>
+          <t>1058522</t>
         </is>
       </c>
       <c r="L664" t="inlineStr">
@@ -41871,17 +41887,17 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>665425.59</t>
+          <t>764507.38</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>21227.02</t>
+          <t>24387.72</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>3658860.09</t>
+          <t>3559778.3</t>
         </is>
       </c>
       <c r="L669" t="inlineStr">
@@ -42057,17 +42073,17 @@
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>1180616.56</t>
+          <t>1346826.03</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>37661.63</t>
+          <t>42963.71</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
         <is>
-          <t>5496787.77</t>
+          <t>5330578.3</t>
         </is>
       </c>
       <c r="L672" t="inlineStr">
@@ -42119,17 +42135,17 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>2131369.55</t>
+          <t>2954652.68</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>96390.99</t>
+          <t>133337.4</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
         <is>
-          <t>9740300.8</t>
+          <t>8917017.67</t>
         </is>
       </c>
       <c r="L673" t="inlineStr">
@@ -42181,17 +42197,17 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>393026.33</t>
+          <t>953832.2</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>14399.44</t>
+          <t>44263.53</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>4164793.31</t>
+          <t>3603987.44</t>
         </is>
       </c>
       <c r="L674" t="inlineStr">
@@ -42615,17 +42631,17 @@
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37119.73</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>660.73</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>896554.67</t>
+          <t>859434.94</t>
         </is>
       </c>
       <c r="L681" t="inlineStr">
@@ -42677,17 +42693,17 @@
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>214292.84</t>
+          <t>239054.05</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>7416.49</t>
+          <t>8177.18</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
         <is>
-          <t>5365047.25</t>
+          <t>5340286.04</t>
         </is>
       </c>
       <c r="L682" t="inlineStr">
@@ -42925,17 +42941,17 @@
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>1947803.4</t>
+          <t>3006253.27</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>303906.11</t>
+          <t>467122.29</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>27355135.72</t>
+          <t>26296685.85</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
@@ -43359,17 +43375,17 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>3037003.32</t>
+          <t>3845384.11</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>294258.62</t>
+          <t>414657.62</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>28776330.83</t>
+          <t>27967950.04</t>
         </is>
       </c>
       <c r="L693" t="inlineStr">
@@ -43545,17 +43561,17 @@
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>3680901.73</t>
+          <t>6582440.06</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>360681.7</t>
+          <t>755978.63</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>38861298.66</t>
+          <t>35959760.33</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
@@ -43607,17 +43623,17 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>3248018.95</t>
+          <t>5896482.97</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>333625.77</t>
+          <t>659103.11</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>31249756.17</t>
+          <t>28601292.15</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -43979,17 +43995,17 @@
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>715278.9</t>
+          <t>2175383.05</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>46212</t>
+          <t>124405.68</t>
         </is>
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>6373126.09</t>
+          <t>4913021.94</t>
         </is>
       </c>
       <c r="L703" t="inlineStr">
@@ -44289,17 +44305,17 @@
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>814834.95</t>
+          <t>1554709.28</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>53166.26</t>
+          <t>92312.4</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>33672474</t>
+          <t>32932599.67</t>
         </is>
       </c>
       <c r="L708" t="inlineStr">
@@ -44475,7 +44491,7 @@
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>245205.74</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
@@ -44485,7 +44501,7 @@
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>11598999.99</t>
+          <t>11353794.25</t>
         </is>
       </c>
       <c r="L711" t="inlineStr">
@@ -44736,7 +44752,11 @@
           <t>41595728.1</t>
         </is>
       </c>
-      <c r="L715" t="inlineStr"/>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>1301606 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -45277,7 +45297,7 @@
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130406.73</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
@@ -45287,7 +45307,7 @@
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>47578995.64</t>
+          <t>47448588.91</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
@@ -45339,7 +45359,7 @@
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94921.2</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
@@ -45349,7 +45369,7 @@
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>2549844</t>
+          <t>2454922.8</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
@@ -45401,17 +45421,17 @@
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>351190.37</t>
+          <t>439013.68</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>115998.15</t>
+          <t>145006.18</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>748534.06</t>
+          <t>660710.75</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
@@ -45463,17 +45483,17 @@
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>8482903.56</t>
+          <t>11015401.85</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>1260901.12</t>
+          <t>1611694.59</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>33165286.83</t>
+          <t>30632788.54</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
@@ -45619,7 +45639,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -45629,12 +45649,12 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 Segmento 2 (835 a 1250), extensão 8,300km</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -45644,22 +45664,22 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>18914979.77</t>
+          <t>9289765.74</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>444194.29</t>
+          <t>22988.6</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>77630.35</t>
+          <t>2641.32</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>18470785.48</t>
+          <t>9266777.14</t>
         </is>
       </c>
       <c r="L730" t="inlineStr">
@@ -45733,17 +45753,17 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -45753,12 +45773,12 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -45768,39 +45788,39 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>26137308.02</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>666248.03</t>
+          <t>444194.29</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>41015.96</t>
+          <t>77630.35</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>25471059.99</t>
+          <t>18470785.48</t>
         </is>
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -45810,17 +45830,17 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
+          <t>Melhoramento e Pavimentação Rodovia Ligação trecho Entrº LMG-690 (Paracatu) - Entrº Entre Ribeiros - Lote 1 - Segmento 1 (0 a 835), extensão: 16,700km</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -45830,27 +45850,27 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>4742883</t>
+          <t>18914979.77</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>77611.93</t>
+          <t>444194.29</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>2863.87</t>
+          <t>77630.35</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>4665271.07</t>
+          <t>18470785.48</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
@@ -45867,7 +45887,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -45877,12 +45897,12 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-120 (B) (Dona Euzébia) - Entrº MGC265, rodovia MG-285 ( Lote 3 - Item 6)</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -45892,22 +45912,22 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>36643741.73</t>
+          <t>26137308.02</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>543643.26</t>
+          <t>666248.03</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>35267</t>
+          <t>41015.96</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>36100098.47</t>
+          <t>25471059.99</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
@@ -45919,12 +45939,12 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -45934,17 +45954,17 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Consultoria</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
+          <t>Elaboração de Projeto de Engenharia Rodoviária de Melhoramentos e Pavimentação do trecho Contorno de Timóteo</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -45954,44 +45974,44 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>4742883</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77611.93</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2863.87</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>25215151.46</t>
+          <t>4665271.07</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DPEI-9520827/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>9520827</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -46001,12 +46021,12 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DE SERVIÇOS DE ESTUDOS TOPOGRÁFICOS (LEVANTAMENTO TOPOGRÁFICO PLANIALTIMÉTRICO E CADASTRAL) EM RODOVIAS SOB JURISDIÇÃO DO DER- MG EM TODO O E</t>
+          <t>Melhoramento da pavimentação e aumento da capacidade do trecho Entrº Piraúba - Entrº Paiva - Rodovia MG-265 - 3ª faixa  (Lote 3 - Item 5)</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>1699613.8</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -46016,39 +46036,39 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>1699613.8</t>
+          <t>36643741.73</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543643.26</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35267</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>1699613.8</t>
+          <t>36100098.47</t>
         </is>
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>2301601 000001/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DPEI-9520825/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9520825</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -46063,12 +46083,12 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DE SERVIÇOS DE ESTUDOS TOPOGRÁFICOS (LEVANTAMENTO TOPOGRÁFICO PLANIALTIMÉTRICO E CADASTRAL) EM RODOVIAS SOB JURISDIÇÃO DO DER- MG EM TODO O E</t>
+          <t>Melhoramento da pavimentação do trecho Entrº MGC-265/MG-452 (p/ Paiva) - Entrº BR-040, rodovia MG-448  (Lote 3 - Item 4)</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>1629000</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -46078,7 +46098,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>1629000</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -46093,24 +46113,24 @@
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>1629000</t>
+          <t>25215151.46</t>
         </is>
       </c>
       <c r="L737" t="inlineStr">
         <is>
-          <t>2301601 000001/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DOV-002/2021-C</t>
+          <t>DPEI-9520827/2026</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>9292040</t>
+          <t>9520827</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -46120,17 +46140,17 @@
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t>EXECUÇÃO DE SERVIÇOS DE ESTUDOS TOPOGRÁFICOS (LEVANTAMENTO TOPOGRÁFICO PLANIALTIMÉTRICO E CADASTRAL) EM RODOVIAS SOB JURISDIÇÃO DO DER- MG EM TODO O E</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>6759878.65</t>
+          <t>1699613.8</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -46140,7 +46160,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>6759878.65</t>
+          <t>1699613.8</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -46155,24 +46175,24 @@
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>6759878.65</t>
+          <t>1699613.8</t>
         </is>
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301601 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>DOV-003/2021-C</t>
+          <t>DPEI-9520825/2026</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>9292042</t>
+          <t>9520825</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -46182,17 +46202,17 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>EXECUÇÃO DE SERVIÇOS DE ESTUDOS TOPOGRÁFICOS (LEVANTAMENTO TOPOGRÁFICO PLANIALTIMÉTRICO E CADASTRAL) EM RODOVIAS SOB JURISDIÇÃO DO DER- MG EM TODO O E</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>7705944.89</t>
+          <t>1629000</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -46202,7 +46222,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>7705944.89</t>
+          <t>1629000</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -46217,24 +46237,24 @@
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>7705944.89</t>
+          <t>1629000</t>
         </is>
       </c>
       <c r="L739" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301601 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>DOV-001/2021-C</t>
+          <t>DOV-002/2021-C</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>9292037</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -46249,12 +46269,12 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>10410721.35</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -46264,7 +46284,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>10410721.35</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -46279,7 +46299,7 @@
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>10410721.35</t>
+          <t>6759878.65</t>
         </is>
       </c>
       <c r="L740" t="inlineStr">
@@ -46291,12 +46311,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>DOV-004/2021-C</t>
+          <t>DOV-003/2021-C</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>9292043</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -46311,12 +46331,12 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>11434972.74</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -46326,7 +46346,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>11434972.74</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -46341,7 +46361,7 @@
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>11434972.74</t>
+          <t>7705944.89</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
@@ -46353,12 +46373,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>DC-9521130/2026</t>
+          <t>DOV-001/2021-C</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>9521130</t>
+          <t>9292037</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -46368,17 +46388,17 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Obra de Arte Especial</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração de Análise de Conformidade para obra de arte especial - Ponte sobre o Rio São Francisco - Entr. MG/161 9 São Romão) - Entr. MG/ 161 (Porto </t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>594297</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -46388,7 +46408,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>594297</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -46403,24 +46423,24 @@
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>594297</t>
+          <t>10410721.35</t>
         </is>
       </c>
       <c r="L742" t="inlineStr">
         <is>
-          <t>2301520 000006/2026</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DOV-004/2021-C</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9292043</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -46435,12 +46455,12 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>11434972.74</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -46450,39 +46470,39 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>47349998.43</t>
+          <t>11434972.74</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>404668.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
         <is>
-          <t>12908.89</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>46945329.59</t>
+          <t>11434972.74</t>
         </is>
       </c>
       <c r="L743" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DC-9521130/2026</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9521130</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -46492,17 +46512,17 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Obra de Arte Especial</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+          <t xml:space="preserve">Elaboração de Análise de Conformidade para obra de arte especial - Ponte sobre o Rio São Francisco - Entr. MG/161 9 São Romão) - Entr. MG/ 161 (Porto </t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -46512,39 +46532,39 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>31699998.96</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>480555.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>14613.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>31219443.24</t>
+          <t>594297</t>
         </is>
       </c>
       <c r="L744" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000006/2026</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>DO-009482032/2025-L6</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -46559,12 +46579,12 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -46574,22 +46594,22 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>35989998.13</t>
+          <t>47349998.43</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>406660.48</t>
+          <t>404668.84</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
         <is>
-          <t>12972.43</t>
+          <t>12908.89</t>
         </is>
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>35583337.65</t>
+          <t>46945329.59</t>
         </is>
       </c>
       <c r="L745" t="inlineStr">
@@ -46601,12 +46621,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -46621,12 +46641,12 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -46636,22 +46656,22 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>23434999.8</t>
+          <t>31699998.96</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>1908611.23</t>
+          <t>480555.72</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>60884.67</t>
+          <t>14613.73</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>21526388.57</t>
+          <t>31219443.24</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
@@ -46663,12 +46683,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -46683,12 +46703,12 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -46698,22 +46718,22 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>32097999.96</t>
+          <t>35989998.13</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>413021.56</t>
+          <t>406660.48</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>13243.17</t>
+          <t>12972.43</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>31684978.4</t>
+          <t>35583337.65</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
@@ -46725,12 +46745,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -46740,17 +46760,17 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -46760,39 +46780,39 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23434999.8</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2387558.2</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76163.07</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21047441.6</t>
         </is>
       </c>
       <c r="L748" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -46802,17 +46822,17 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -46822,39 +46842,39 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32097999.96</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>413021.56</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13243.17</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31684978.4</t>
         </is>
       </c>
       <c r="L749" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>9519595</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -46869,12 +46889,12 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -46884,7 +46904,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46899,24 +46919,24 @@
       </c>
       <c r="K750" t="inlineStr">
         <is>
-          <t>69497864.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L750" t="inlineStr">
         <is>
-          <t>2301520 000037/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -46926,17 +46946,17 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -46946,39 +46966,39 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>14264750.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>11405231.61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>514749.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>2859519.21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L751" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -46988,59 +47008,59 @@
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+          <t>Execução das obras de Melhoramento e pavimento - Trecho: Araçaí - Sete Lagoas - Rodovia Municipal,  com 25,250 km de extensão</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>32998445.8</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>105606.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>33104051.9</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>5091753.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>731575.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>28012298.67</t>
+          <t>69497864.4</t>
         </is>
       </c>
       <c r="L752" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000037/2026</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -47050,17 +47070,17 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
+          <t>Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -47070,39 +47090,39 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>14264750.82</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11842385.79</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>536513.46</t>
         </is>
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>2422365.03</t>
         </is>
       </c>
       <c r="L753" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>VD - 9513686/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>9513686</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -47112,59 +47132,59 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>32998445.8</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105606.1</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>33104051.9</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5091753.23</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>731575.94</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
         <is>
-          <t>29652999.54</t>
+          <t>28012298.67</t>
         </is>
       </c>
       <c r="L754" t="inlineStr">
         <is>
-          <t>2301001 000001/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>DM-9437231-A</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>9437231</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -47174,17 +47194,17 @@
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 02ª URG</t>
+          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>48698697.21</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -47194,7 +47214,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>48698697.21</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -47209,24 +47229,24 @@
       </c>
       <c r="K755" t="inlineStr">
         <is>
-          <t>48698697.21</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="L755" t="inlineStr">
         <is>
-          <t>2301762 000006/2024</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>VD - 9513686/2026</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9513686</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -47236,17 +47256,17 @@
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
+          <t>Contratação de empresa de engenharia para execução de serviços de natureza contínua de sinalização viária vertical, horizontal e dispositivos auxiliar</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -47256,39 +47276,39 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>120800000</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>5110057.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>139646.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
         <is>
-          <t>115689942.12</t>
+          <t>29652999.54</t>
         </is>
       </c>
       <c r="L756" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>2301001 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DM-9437231-A</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9437231</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -47298,17 +47318,17 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recuperação Funcional </t>
+          <t>Manutenção Rodoviária</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 02ª URG</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>48698697.21</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
@@ -47318,39 +47338,39 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>14124998.39</t>
+          <t>48698697.21</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>3294350.69</t>
+          <t>1202010.87</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>82624.61</t>
+          <t>108025.11</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>10830647.7</t>
+          <t>47496686.34</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000006/2024</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>DC-9519740/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>9519740</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -47365,12 +47385,12 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do Contorno de Andradas, em rodovia de contorno, sob jurisdição do DER-MG</t>
+          <t>Complemento de obras - Melhoramento e Pavimentação do Trecho: Januária - Pandeiros, Rodovia: MGC/479, com extensão de 46,000 km</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -47380,37 +47400,41 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>120800000</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7068639.14</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244973.1</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
         <is>
-          <t>27896726.26</t>
+          <t>113731360.86</t>
         </is>
       </c>
       <c r="L758" t="inlineStr">
         <is>
-          <t>2301520 000040/2026</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B759" t="inlineStr"/>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>9500304</t>
+        </is>
+      </c>
       <c r="C759" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -47418,17 +47442,17 @@
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t xml:space="preserve">Recuperação Funcional </t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
+          <t>Recuperação funcional MG-314, Entrº para Virgolândia - Entrº MGC-259 para Gov. Valadares</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -47438,35 +47462,39 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>1768342.65</t>
+          <t>14124998.39</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>361647.49</t>
+          <t>3294350.69</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>1844.4</t>
+          <t>82624.61</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
         <is>
-          <t>1406695.16</t>
-        </is>
-      </c>
-      <c r="L759" t="inlineStr"/>
+          <t>10830647.7</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>2301762 000027/2025</t>
+        </is>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9519740/2026</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9519740</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -47476,59 +47504,59 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t>Melhoramento e pavimentação do Contorno de Andradas, em rodovia de contorno, sob jurisdição do DER-MG</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>27896726.26</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>2915216.97</t>
+          <t>942062.72</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
         <is>
-          <t>92995.38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>34249515.26</t>
+          <t>26954663.54</t>
         </is>
       </c>
       <c r="L760" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000040/2026</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>AMA-9502187/2026</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9502187</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -47538,59 +47566,59 @@
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Supervisão</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>36033198.22</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>1131534.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>37164732.23</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>2915216.97</t>
+          <t>452059.37</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>92995.38</t>
+          <t>3688.8</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
         <is>
-          <t>34249515.26</t>
+          <t>1316283.28</t>
         </is>
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>AMA-9502187/2026</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9502187</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -47600,17 +47628,17 @@
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+          <t xml:space="preserve">Elaboração do Estudo do Componente Indígena (ECI) e Plano Básico Ambiental Indígena (PBAI) para anuência da Fundação Nacional dos Povos Indígenas. </t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -47620,39 +47648,39 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>1768342.65</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>452059.37</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3688.8</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>45188997.86</t>
+          <t>1316283.28</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000004/2025</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -47662,59 +47690,59 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>77898894.3</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>467698.96</t>
+          <t>2915216.97</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>15952.15</t>
+          <t>92995.38</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>77431195.34</t>
+          <t>34249515.26</t>
         </is>
       </c>
       <c r="L763" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -47724,59 +47752,59 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Supervisão</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
+          <t>Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>36033198.22</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1131534.01</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>44002130</t>
+          <t>37164732.23</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>2125636.51</t>
+          <t>2915216.97</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92995.38</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
         <is>
-          <t>41876493.49</t>
+          <t>34249515.26</t>
         </is>
       </c>
       <c r="L764" t="inlineStr">
         <is>
-          <t>2301762 000004/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>9518942</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -47786,17 +47814,17 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Rodovia</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -47806,12 +47834,12 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>61779996.11</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>13200.81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -47821,24 +47849,24 @@
       </c>
       <c r="K765" t="inlineStr">
         <is>
-          <t>61766795.3</t>
+          <t>45188997.86</t>
         </is>
       </c>
       <c r="L765" t="inlineStr">
         <is>
-          <t>2301520 000011/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -47848,17 +47876,17 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+          <t>Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
         </is>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -47868,39 +47896,39 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>24832463.21</t>
+          <t>77898894.3</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>4336664.12</t>
+          <t>467698.96</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>654013.33</t>
+          <t>15952.15</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
         <is>
-          <t>20495799.09</t>
+          <t>77431195.34</t>
         </is>
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -47915,12 +47943,12 @@
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 06ª URG</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -47930,39 +47958,39 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>34422078.35</t>
+          <t>44002130</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>7934404.13</t>
+          <t>3329407.24</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
         <is>
-          <t>1101483.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K767" t="inlineStr">
         <is>
-          <t>26487674.22</t>
+          <t>40672722.76</t>
         </is>
       </c>
       <c r="L767" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9518942</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -47972,17 +48000,17 @@
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>Manutenção Rodoviária</t>
+          <t>Rodovia</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+          <t xml:space="preserve">Complementação da obra na Rodovia LMG-680, trecho LMG-690 (Paracatu) Entrº Entre Ribeiros - Entrº MG-181 - Estaca: 2550 a 3281, em Rodovia Municipal, </t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>61779996.11</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -47992,87 +48020,273 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>30603197.87</t>
+          <t>61779996.11</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>5874286.21</t>
+          <t>304399.06</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>751156.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>24728911.66</t>
+          <t>61475597.05</t>
         </is>
       </c>
       <c r="L768" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>24832463.21</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>4336664.12</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>654013.33</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>20495799.09</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>9418600</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>34422078.35</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>7934404.13</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>1101483.73</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>26487674.22</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Manutenção Rodoviária</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>30603197.87</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>5874286.21</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>751156.76</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>24728911.66</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
           <t>DM-008/2024-A</t>
         </is>
       </c>
-      <c r="B769" t="inlineStr">
+      <c r="B772" t="inlineStr">
         <is>
           <t>9422064</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D769" t="inlineStr">
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
         <is>
           <t>Manutenção Rodoviária</t>
         </is>
       </c>
-      <c r="E769" t="inlineStr">
+      <c r="E772" t="inlineStr">
         <is>
           <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
-      <c r="F769" t="inlineStr">
+      <c r="F772" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="G769" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H769" t="inlineStr">
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
         <is>
           <t>31172534.58</t>
         </is>
       </c>
-      <c r="I769" t="inlineStr">
+      <c r="I772" t="inlineStr">
         <is>
           <t>6708321.8</t>
         </is>
       </c>
-      <c r="J769" t="inlineStr">
+      <c r="J772" t="inlineStr">
         <is>
           <t>857116.51</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr">
+      <c r="K772" t="inlineStr">
         <is>
           <t>24464212.78</t>
         </is>
       </c>
-      <c r="L769" t="inlineStr">
+      <c r="L772" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
         </is>
